--- a/docs/Files/Small-format_model/ODYM_T6_ToUsedExportRate_V1.0.xlsx
+++ b/docs/Files/Small-format_model/ODYM_T6_ToUsedExportRate_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F45663-0FF6-4DA3-911C-EDDFF9D7CB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F5F753-D1FC-4013-A000-C585BDEF3719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -330,18 +330,12 @@
     <t>Share of after use flow going to used export</t>
   </si>
   <si>
-    <t>EV LIB</t>
-  </si>
-  <si>
     <t>LIB</t>
   </si>
   <si>
     <t>LIB scrap</t>
   </si>
   <si>
-    <t>other EV LIB products</t>
-  </si>
-  <si>
     <t>LIB materials</t>
   </si>
   <si>
@@ -355,6 +349,12 @@
   </si>
   <si>
     <t>ODYM_Classifications_SF</t>
+  </si>
+  <si>
+    <t>SF LIB</t>
+  </si>
+  <si>
+    <t>other SF LIB products</t>
   </si>
 </sst>
 </file>
@@ -908,7 +908,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -1006,7 +1006,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1234,16 +1234,16 @@
         <v>55</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" t="s">
         <v>99</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="E2">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1255,7 +1255,7 @@
         <v>54</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -1263,16 +1263,16 @@
         <v>55</v>
       </c>
       <c r="B3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="E3">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1284,7 +1284,7 @@
         <v>54</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
